--- a/user-templates/DEV/AT - AT Testing.xlsx
+++ b/user-templates/DEV/AT - AT Testing.xlsx
@@ -110,7 +110,7 @@
     <t>UOM</t>
   </si>
   <si>
-    <t>50473580</t>
+    <t>50473607</t>
   </si>
   <si>
     <t>FERT</t>
